--- a/cadifa_completo_anterior.xlsx
+++ b/cadifa_completo_anterior.xlsx
@@ -2084,7 +2084,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>001.1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>002.1</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">

--- a/cadifa_completo_anterior.xlsx
+++ b/cadifa_completo_anterior.xlsx
@@ -446,16 +446,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
+          <t>Xellia Pharmaceuticals Aps</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cloridrato de sertralina</t>
+          <t>anfotericina b</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.535111417920225e+16</v>
+        <v>2.535186061720232e+16</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -464,23 +464,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
+          <t>Wanbury Limited</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>propionato de fluticasona</t>
+          <t>cloridrato de metformina</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.535108802020242e+16</v>
+        <v>2.535145491320248e+16</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -489,23 +489,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
+          <t>Honour Lab Limited</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>levetiracetam</t>
+          <t>empagliflozina</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.535107861420242e+16</v>
+        <v>2.535142787520248e+16</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -514,23 +514,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
+          <t>Asolution Pharmaceuticals Pvt. Ltd.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>vismodegibe</t>
+          <t>sugamadex sódico</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.535104597120268e+16</v>
+        <v>2.535179383020215e+16</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -539,23 +539,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shilpa Pharma Lifesciences Limited</t>
+          <t>Hetero Labs Limited</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mesilato de lenvatinibe</t>
+          <t>cloridrato de atomoxetina</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.535101727520259e+16</v>
+        <v>2.535111432020255e+16</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -564,23 +564,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hetero Labs Limited</t>
+          <t>Sun Pharmaceutical Industries Limited</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cloridrato de atomoxetina</t>
+          <t>lacosamida</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.535111432020255e+16</v>
+        <v>2.535122646420255e+16</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -589,23 +589,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Asolution Pharmaceuticals Pvt. Ltd.</t>
+          <t>Harman Finochem Limited</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sugamadex sódico</t>
+          <t>hemitartarato de norepinefrina monoidratada</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.535179383020215e+16</v>
+        <v>2.535135869320245e+16</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -614,23 +614,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Harman Finochem Limited</t>
+          <t>Synthon Bv</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hemitartarato de norepinefrina monoidratada</t>
+          <t>lenalidomida</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.535135869320245e+16</v>
+        <v>2.535180785020239e+16</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -639,23 +639,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Synthon Bv</t>
+          <t>Sun Pharmaceutical Industries Limited</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>lenalidomida</t>
+          <t>dapagliflozina propanodiol monoidratado</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.535180785020239e+16</v>
+        <v>2.535135509020241e+16</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -664,23 +664,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
+          <t>Hetero Drugs Limited</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>lacosamida</t>
+          <t>mirtazapina</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.535122646420255e+16</v>
+        <v>2.535126854620231e+16</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -689,23 +689,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Wanbury Limited</t>
+          <t>Sun Pharmaceutical Industries Limited</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>cloridrato de metformina</t>
+          <t>cloridrato de sertralina</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.535145491320248e+16</v>
+        <v>2.535111417920225e+16</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -714,23 +714,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Honour Lab Limited</t>
+          <t>Sun Pharmaceutical Industries Limited</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>empagliflozina</t>
+          <t>propionato de fluticasona</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.535142787520248e+16</v>
+        <v>2.535108802020242e+16</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -739,23 +739,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hetero Drugs Limited</t>
+          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mirtazapina</t>
+          <t>levetiracetam</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.535126854620231e+16</v>
+        <v>2.535107861420242e+16</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -776,11 +776,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dapagliflozina propanodiol monoidratado</t>
+          <t>vismodegibe</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.535135509020241e+16</v>
+        <v>2.535104597120268e+16</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -789,23 +789,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Xellia Pharmaceuticals Aps</t>
+          <t>Shilpa Pharma Lifesciences Limited</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>anfotericina b</t>
+          <t>mesilato de lenvatinibe</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.535186061720232e+16</v>
+        <v>2.535101727520259e+16</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>

--- a/cadifa_completo_anterior.xlsx
+++ b/cadifa_completo_anterior.xlsx
@@ -896,7 +896,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Heraeus Deutschland Gmbh &amp; Co. Kg</t>
+          <t>Heraeus Precious Metals Gmbh &amp; Co. Kg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>001.1</t>
+          <t>001</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">

--- a/cadifa_completo_anterior.xlsx
+++ b/cadifa_completo_anterior.xlsx
@@ -12721,7 +12721,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Zhejiang Supor Pharmaceuticals Co., Ltd</t>
+          <t>Zhejiang Syncotide Bio-Pharmaceutical Co., Ltd.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">

--- a/cadifa_completo_anterior.xlsx
+++ b/cadifa_completo_anterior.xlsx
@@ -5834,7 +5834,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>001.1</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
